--- a/processed_file.xlsx
+++ b/processed_file.xlsx
@@ -14,126 +14,231 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="40">
-  <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
-    <t>2025-01-02</t>
-  </si>
-  <si>
-    <t>2025-01-03</t>
-  </si>
-  <si>
-    <t>2025-01-04</t>
-  </si>
-  <si>
-    <t>2025-01-05</t>
-  </si>
-  <si>
-    <t>2025-01-07</t>
-  </si>
-  <si>
-    <t>2025-01-08</t>
-  </si>
-  <si>
-    <t>2025-01-09</t>
-  </si>
-  <si>
-    <t>2025-01-10</t>
-  </si>
-  <si>
-    <t>2025-01-11</t>
-  </si>
-  <si>
-    <t>2025-01-12</t>
-  </si>
-  <si>
-    <t>2025-01-14</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="75">
   <si>
     <t>2025-01-16</t>
   </si>
   <si>
-    <t>2025-01-17</t>
-  </si>
-  <si>
-    <t>2025-01-18</t>
-  </si>
-  <si>
-    <t>2025-01-19</t>
-  </si>
-  <si>
     <t>2025-01-22</t>
   </si>
   <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>2025-01-28</t>
-  </si>
-  <si>
-    <t>RECEBIMENTOS N/DATA</t>
-  </si>
-  <si>
-    <t>VLR. RECEBIDO D.A. 3146571 F-31941 0 WAGNER DE AGUIAR - 02/01/2025</t>
-  </si>
-  <si>
-    <t>VLR. RECEBIDO D.A. 3146573 F-31941 0 WAGNER DE AGUIAR 2024-12-17 00:00:00</t>
-  </si>
-  <si>
-    <t>VLR. RECEBIDO D.A. 3146574 F-31941 0 WAGNER DE AGUIAR 2024-12-19 00:00:00</t>
-  </si>
-  <si>
-    <t>VLR. RECEBIDO D.A. 3146578 F-31941 0 WAGNER DE AGUIAR - 20/12/2024</t>
-  </si>
-  <si>
-    <t>VLR. RECEBIDO D.A. 3146579 F-31941 0 WAGNER DE AGUIAR 2024-12-21 00:00:00</t>
-  </si>
-  <si>
-    <t>VLR. RECEBIDO D.A. 3146581 F-31941 0 WAGNER DE AGUIAR - 27/12/2024</t>
-  </si>
-  <si>
-    <t>VLR. RECEBIDO D.A. 3146582 F-31941 0 WAGNER DE AGUIAR - 28/12/2024</t>
-  </si>
-  <si>
-    <t>VLR. RECEBIDO D.A. 3146583 F-31941 0 WAGNER DE AGUIAR - 31/12/2024</t>
-  </si>
-  <si>
-    <t>VLR. RECEBIDO D.A. 3146586 F-31941 0 WAGNER DE AGUIAR - COMPLEMENTO 20/12/2024</t>
-  </si>
-  <si>
-    <t>VLR. TRANSF. DA CONTA 33257 P/ 16,  REF. ENTRADA DE CAIXA GOLFE DIAS 17,19,20,21,27,28,31 DE DEZEMBRO DE 2024 E 02/01/2025 - DA 3147060</t>
-  </si>
-  <si>
-    <t>PAGAMENTOS N/DATA</t>
-  </si>
-  <si>
-    <t>VLR. RECEBIDO D.A. 3148034 F-31941 0 WAGNER DE AGUIAR - 08/01/2025</t>
-  </si>
-  <si>
-    <t>VLR. RECEBIDO D.A. 3148035 F-31941 0 WAGNER DE AGUIAR - 14/01/2025</t>
-  </si>
-  <si>
-    <t>VLR. RECEBIDO D.A. 3148036 F-31941 0 WAGNER DE AGUIAR - 12/01/2025</t>
-  </si>
-  <si>
-    <t>VLR. RECEBIDO D.A. 3148037 F-31941 0 WAGNER DE AGUIAR - 11/01/2025</t>
-  </si>
-  <si>
-    <t>VLR. RECEBIDO D.A. 3148038 F-31941 0 WAGNER DE AGUIAR - 10/01/2025</t>
-  </si>
-  <si>
-    <t>VLR. RECEBIDO D.A. 3148039 F-31941 0 WAGNER DE AGUIAR - 07/01/2025</t>
-  </si>
-  <si>
-    <t>VLR. TRANSF. DA CONTA 33257 P/ 16,  REF. ENTRADA DE CAIXA GOLFE DIAS 07,08,10,11,12,E 14 DE JANEIRO DE 2025 - DA 3148058</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>33257</t>
+    <t>2025-01-30</t>
+  </si>
+  <si>
+    <t>2025-01-31</t>
+  </si>
+  <si>
+    <t>2025-02-03</t>
+  </si>
+  <si>
+    <t>2025-02-04</t>
+  </si>
+  <si>
+    <t>2025-02-05</t>
+  </si>
+  <si>
+    <t>2025-02-06</t>
+  </si>
+  <si>
+    <t>2025-02-07</t>
+  </si>
+  <si>
+    <t>2025-02-08</t>
+  </si>
+  <si>
+    <t>2025-02-10</t>
+  </si>
+  <si>
+    <t>2025-02-11</t>
+  </si>
+  <si>
+    <t>2025-02-12</t>
+  </si>
+  <si>
+    <t>2025-02-13</t>
+  </si>
+  <si>
+    <t>2025-02-14</t>
+  </si>
+  <si>
+    <t>2025-02-17</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3061614/3061613</t>
+  </si>
+  <si>
+    <t>N/PGTO. REF. DEVOLUÇÃO D.A. 3146336 B-5940 5 AUGUSTO TORMENA MOREIRA (MARCOS DE OLIVEIRA MOREIRA)</t>
+  </si>
+  <si>
+    <t>N/PGTO. REF. DEVOLUÇÃO D.A. 3147126 B-4669 0 FRANCISCO M DE PAULA XAVIER</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3046187</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3060707</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS VINDI/GALAX D.A. 3061448/3061117/3060824/3046921/3046491</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS VINDI/GALAX D.A. 3063473</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3152390</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152598/3152599/3152947</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152774/3152694</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152093/3152177</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3152317/3152740/3153061</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3152497/3152920/3152292</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3151937</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3154143/3152823</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3060523/3153112/3153308</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3152551/3151823</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152845</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152827</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3153030</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3154236</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3046434</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3151858</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152676/3152677</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3151789/3151778/3153106/3151819/3151790</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3046579</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152541</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3152461/3153143/3152409/3152993/3153093/3152809/3152862</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152558</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152524</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152641</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152884</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3151850/3151851/3151860/3151868/3151899/3151902/3151903/31 51971/3151989/3152008/3152054/3152059/3152191/3152199/3152 204/3152214/3152245/3152263/3152355/3152428/3152531/315253 5/3152539/3152573</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3152585/3152600/3152613/3152620/3152626/3152627/3152630/31 52631/3152633/3152634/3152642/3152654/3152680/3152691/3152 697/3152717/3152729/3152737/3152825/3152831/3152832/315284 9/3152850/3152851</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3152853/3152857/3152865/3152866/3152870/3152871/3152898/31 52907/3152908/3152918/3152936/3152946/3152954/3152960/3153 097/3153120/3155141</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3152358/3152382</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3151856/3152965/3152782/3061588/3152089/3152889/3151834/31 52388/3151835/3151855/3153130/3152888/3151930/3047253/3152 964</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3152151</t>
+  </si>
+  <si>
+    <t>VLR. RECEBIDO D.A. 3152180</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3153302</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152602</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3151996/3152608/3155361/3155415</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3152277</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3061774/3152287/3155350/3152751</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3152061/3155138/3155447</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3144244/3152128</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3152738/3152756</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152372</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152321</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3153160/3156088</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3152344</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3152858/3152725/3152812/3152778/3152308/3152251</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS VINDI/GALAX D.A. 3152259/3152202/3152750/3152068/3152952/3152216/3152912/31 52078/3152720/3152727/3152726/3152785/3155517/3155371/3151 876/3152923/3151770/3152743/3046199/3152742</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS VINDI/GALAX D.A. 3155673/3152479/3152230/3152268</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS VINDI/GALAX D.A. 3152526/3152057/3153084/3152728/3152596/3152442/3046266/31 52961/3152902/3152478/3152667/3152874/3152628/3151911/31521 54</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3155152</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3155153</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>22176</t>
   </si>
 </sst>
 </file>
@@ -465,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -473,389 +578,389 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D1">
-        <v>6062</v>
+        <v>223</v>
       </c>
       <c r="E1">
-        <v>17</v>
-      </c>
-      <c r="F1">
-        <v>850</v>
+        <v>25</v>
+      </c>
+      <c r="G1">
+        <v>548</v>
       </c>
       <c r="H1">
-        <v>2698</v>
+        <v>4429.63</v>
       </c>
       <c r="I1" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D2">
-        <v>155</v>
+        <v>241</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F2">
-        <v>162</v>
+        <v>102</v>
       </c>
       <c r="H2">
-        <v>2860</v>
+        <v>4327.63</v>
       </c>
       <c r="I2" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J2" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3">
-        <v>159</v>
+        <v>372</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="F3">
-        <v>99</v>
+        <v>83.63</v>
       </c>
       <c r="H3">
-        <v>2959</v>
+        <v>4244</v>
       </c>
       <c r="I3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J3" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="D4">
-        <v>163</v>
+        <v>467</v>
       </c>
       <c r="E4">
-        <v>19</v>
-      </c>
-      <c r="F4">
-        <v>222</v>
+        <v>17</v>
+      </c>
+      <c r="G4">
+        <v>196</v>
       </c>
       <c r="H4">
-        <v>3181</v>
+        <v>4440</v>
       </c>
       <c r="I4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J4" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5">
-        <v>167</v>
+        <v>478</v>
       </c>
       <c r="E5">
-        <v>13</v>
-      </c>
-      <c r="F5">
-        <v>10</v>
+        <v>17</v>
+      </c>
+      <c r="G5">
+        <v>196</v>
       </c>
       <c r="H5">
-        <v>3191</v>
+        <v>4636</v>
       </c>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J5" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D6">
-        <v>172</v>
+        <v>502</v>
       </c>
       <c r="E6">
-        <v>13</v>
-      </c>
-      <c r="F6">
-        <v>100</v>
+        <v>61</v>
+      </c>
+      <c r="G6">
+        <v>980</v>
       </c>
       <c r="H6">
-        <v>3291</v>
+        <v>5616</v>
       </c>
       <c r="I6" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J6" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D7">
-        <v>177</v>
+        <v>502</v>
       </c>
       <c r="E7">
-        <v>19</v>
-      </c>
-      <c r="F7">
-        <v>171</v>
+        <v>66</v>
+      </c>
+      <c r="G7">
+        <v>34</v>
       </c>
       <c r="H7">
-        <v>3462</v>
+        <v>5650</v>
       </c>
       <c r="I7" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J7" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D8">
-        <v>179</v>
+        <v>480</v>
       </c>
       <c r="E8">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>162</v>
+        <v>204</v>
       </c>
       <c r="H8">
-        <v>3300</v>
+        <v>5854</v>
       </c>
       <c r="I8" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J8" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D9">
-        <v>179</v>
+        <v>509</v>
       </c>
       <c r="E9">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="G9">
-        <v>160</v>
+        <v>612</v>
       </c>
       <c r="H9">
-        <v>3140</v>
+        <v>6466</v>
       </c>
       <c r="I9" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J9" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D10">
-        <v>179</v>
+        <v>512</v>
       </c>
       <c r="E10">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G10">
-        <v>220</v>
+        <v>571</v>
       </c>
       <c r="H10">
-        <v>2920</v>
+        <v>7037</v>
       </c>
       <c r="I10" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J10" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D11">
-        <v>179</v>
+        <v>512</v>
       </c>
       <c r="E11">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G11">
-        <v>320</v>
+        <v>396</v>
       </c>
       <c r="H11">
-        <v>2600</v>
+        <v>7433</v>
       </c>
       <c r="I11" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J11" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D12">
-        <v>179</v>
+        <v>619</v>
       </c>
       <c r="E12">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G12">
-        <v>710</v>
+        <v>612</v>
       </c>
       <c r="H12">
-        <v>1890</v>
+        <v>8045</v>
       </c>
       <c r="I12" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J12" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D13">
-        <v>179</v>
+        <v>637</v>
       </c>
       <c r="E13">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G13">
-        <v>60</v>
+        <v>612</v>
       </c>
       <c r="H13">
-        <v>1830</v>
+        <v>8657</v>
       </c>
       <c r="I13" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J13" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D14">
-        <v>179</v>
+        <v>720</v>
       </c>
       <c r="E14">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G14">
-        <v>120</v>
+        <v>204</v>
       </c>
       <c r="H14">
-        <v>1710</v>
+        <v>8861</v>
       </c>
       <c r="I14" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J14" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D15">
-        <v>179</v>
+        <v>721</v>
       </c>
       <c r="E15">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="G15">
-        <v>850</v>
+        <v>408</v>
       </c>
       <c r="H15">
-        <v>860</v>
+        <v>9269</v>
       </c>
       <c r="I15" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J15" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -863,571 +968,1091 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D16">
-        <v>179</v>
+        <v>621</v>
       </c>
       <c r="E16">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G16">
-        <v>65</v>
+        <v>767</v>
       </c>
       <c r="H16">
-        <v>795</v>
+        <v>10036</v>
       </c>
       <c r="I16" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J16" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D17">
-        <v>182</v>
+        <v>638</v>
       </c>
       <c r="E17">
-        <v>5</v>
-      </c>
-      <c r="F17">
-        <v>2667</v>
+        <v>19</v>
+      </c>
+      <c r="G17">
+        <v>408</v>
       </c>
       <c r="H17">
-        <v>3462</v>
+        <v>10444</v>
       </c>
       <c r="I17" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J17" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18">
+        <v>724</v>
+      </c>
+      <c r="E18">
         <v>7</v>
       </c>
-      <c r="B18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18">
-        <v>182</v>
-      </c>
-      <c r="E18">
-        <v>9</v>
-      </c>
       <c r="G18">
-        <v>2667</v>
+        <v>204</v>
       </c>
       <c r="H18">
-        <v>795</v>
+        <v>10648</v>
       </c>
       <c r="I18" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J18" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D19">
-        <v>187</v>
+        <v>725</v>
       </c>
       <c r="E19">
-        <v>17</v>
-      </c>
-      <c r="F19">
-        <v>132</v>
+        <v>29</v>
+      </c>
+      <c r="G19">
+        <v>204</v>
       </c>
       <c r="H19">
-        <v>927</v>
+        <v>10852</v>
       </c>
       <c r="I19" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J19" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D20">
-        <v>191</v>
+        <v>725</v>
       </c>
       <c r="E20">
-        <v>10</v>
-      </c>
-      <c r="F20">
-        <v>150</v>
+        <v>30</v>
+      </c>
+      <c r="G20">
+        <v>204</v>
       </c>
       <c r="H20">
-        <v>1077</v>
+        <v>11056</v>
       </c>
       <c r="I20" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J20" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D21">
-        <v>194</v>
+        <v>623</v>
       </c>
       <c r="E21">
-        <v>14</v>
-      </c>
-      <c r="F21">
-        <v>227</v>
+        <v>34</v>
+      </c>
+      <c r="G21">
+        <v>153</v>
       </c>
       <c r="H21">
-        <v>1304</v>
+        <v>11209</v>
       </c>
       <c r="I21" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J21" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="D22">
-        <v>199</v>
+        <v>677</v>
       </c>
       <c r="E22">
-        <v>9</v>
-      </c>
-      <c r="F22">
-        <v>33</v>
+        <v>23</v>
+      </c>
+      <c r="G22">
+        <v>196</v>
       </c>
       <c r="H22">
-        <v>1337</v>
+        <v>11405</v>
       </c>
       <c r="I22" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J22" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D23">
-        <v>239</v>
+        <v>730</v>
       </c>
       <c r="E23">
         <v>13</v>
       </c>
-      <c r="F23">
-        <v>100</v>
+      <c r="G23">
+        <v>204</v>
       </c>
       <c r="H23">
-        <v>1437</v>
+        <v>11609</v>
       </c>
       <c r="I23" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J23" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D24">
-        <v>241</v>
+        <v>732</v>
       </c>
       <c r="E24">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="G24">
-        <v>171</v>
+        <v>408</v>
       </c>
       <c r="H24">
-        <v>1266</v>
+        <v>12017</v>
       </c>
       <c r="I24" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J24" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D25">
-        <v>241</v>
+        <v>639</v>
       </c>
       <c r="E25">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G25">
-        <v>33</v>
+        <v>1020</v>
       </c>
       <c r="H25">
-        <v>1233</v>
+        <v>13037</v>
       </c>
       <c r="I25" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J25" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D26">
-        <v>241</v>
+        <v>735</v>
       </c>
       <c r="E26">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G26">
-        <v>227</v>
+        <v>196</v>
       </c>
       <c r="H26">
-        <v>1006</v>
+        <v>13233</v>
       </c>
       <c r="I26" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J26" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D27">
-        <v>241</v>
+        <v>741</v>
       </c>
       <c r="E27">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G27">
-        <v>150</v>
+        <v>204</v>
       </c>
       <c r="H27">
-        <v>856</v>
+        <v>13437</v>
       </c>
       <c r="I27" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J27" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D28">
-        <v>241</v>
+        <v>640</v>
       </c>
       <c r="E28">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="G28">
-        <v>132</v>
+        <v>1591</v>
       </c>
       <c r="H28">
-        <v>724</v>
+        <v>15028</v>
       </c>
       <c r="I28" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J28" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D29">
-        <v>241</v>
+        <v>744</v>
       </c>
       <c r="E29">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G29">
-        <v>100</v>
+        <v>204</v>
       </c>
       <c r="H29">
-        <v>624</v>
+        <v>15232</v>
       </c>
       <c r="I29" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J29" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D30">
-        <v>298</v>
+        <v>744</v>
       </c>
       <c r="E30">
-        <v>4</v>
-      </c>
-      <c r="F30">
-        <v>813</v>
+        <v>21</v>
+      </c>
+      <c r="G30">
+        <v>204</v>
       </c>
       <c r="H30">
-        <v>1437</v>
+        <v>15436</v>
       </c>
       <c r="I30" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J30" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D31">
-        <v>298</v>
+        <v>748</v>
       </c>
       <c r="E31">
-        <v>11</v>
-      </c>
-      <c r="F31">
-        <v>88</v>
+        <v>54</v>
+      </c>
+      <c r="G31">
+        <v>204</v>
       </c>
       <c r="H31">
-        <v>1525</v>
+        <v>15640</v>
       </c>
       <c r="I31" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J31" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="D32">
-        <v>298</v>
+        <v>748</v>
       </c>
       <c r="E32">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="G32">
-        <v>813</v>
+        <v>204</v>
       </c>
       <c r="H32">
-        <v>712</v>
+        <v>15844</v>
       </c>
       <c r="I32" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J32" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="D33">
-        <v>302</v>
+        <v>629</v>
       </c>
       <c r="E33">
-        <v>14</v>
-      </c>
-      <c r="F33">
-        <v>252</v>
+        <v>71</v>
+      </c>
+      <c r="G33">
+        <v>5711</v>
       </c>
       <c r="H33">
-        <v>964</v>
+        <v>21555</v>
       </c>
       <c r="I33" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J33" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="D34">
-        <v>304</v>
+        <v>629</v>
       </c>
       <c r="E34">
-        <v>10</v>
-      </c>
-      <c r="F34">
-        <v>32</v>
+        <v>72</v>
+      </c>
+      <c r="G34">
+        <v>5222</v>
       </c>
       <c r="H34">
-        <v>996</v>
+        <v>26777</v>
       </c>
       <c r="I34" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J34" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D35">
-        <v>357</v>
+        <v>629</v>
       </c>
       <c r="E35">
-        <v>11</v>
-      </c>
-      <c r="F35">
-        <v>22</v>
+        <v>73</v>
+      </c>
+      <c r="G35">
+        <v>3417</v>
       </c>
       <c r="H35">
-        <v>1018</v>
+        <v>30194</v>
       </c>
       <c r="I35" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J35" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="D36">
-        <v>365</v>
+        <v>629</v>
       </c>
       <c r="E36">
-        <v>20</v>
-      </c>
-      <c r="F36">
-        <v>1178</v>
+        <v>82</v>
+      </c>
+      <c r="G36">
+        <v>508</v>
       </c>
       <c r="H36">
-        <v>2196</v>
+        <v>30702</v>
       </c>
       <c r="I36" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="J36" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37">
+        <v>641</v>
+      </c>
+      <c r="E37">
+        <v>37</v>
+      </c>
+      <c r="G37">
+        <v>3207</v>
+      </c>
+      <c r="H37">
+        <v>33909</v>
+      </c>
+      <c r="I37" t="s">
+        <v>73</v>
+      </c>
+      <c r="J37" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38">
+        <v>641</v>
+      </c>
+      <c r="E38">
+        <v>47</v>
+      </c>
+      <c r="G38">
+        <v>254</v>
+      </c>
+      <c r="H38">
+        <v>34163</v>
+      </c>
+      <c r="I38" t="s">
+        <v>73</v>
+      </c>
+      <c r="J38" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" t="s">
+        <v>54</v>
+      </c>
+      <c r="D39">
+        <v>750</v>
+      </c>
+      <c r="E39">
+        <v>9</v>
+      </c>
+      <c r="G39">
+        <v>204</v>
+      </c>
+      <c r="H39">
+        <v>34367</v>
+      </c>
+      <c r="I39" t="s">
+        <v>73</v>
+      </c>
+      <c r="J39" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40">
+        <v>750</v>
+      </c>
+      <c r="E40">
+        <v>10</v>
+      </c>
+      <c r="G40">
+        <v>204</v>
+      </c>
+      <c r="H40">
+        <v>34571</v>
+      </c>
+      <c r="I40" t="s">
+        <v>73</v>
+      </c>
+      <c r="J40" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41">
+        <v>753</v>
+      </c>
+      <c r="E41">
+        <v>58</v>
+      </c>
+      <c r="G41">
+        <v>204</v>
+      </c>
+      <c r="H41">
+        <v>34775</v>
+      </c>
+      <c r="I41" t="s">
+        <v>73</v>
+      </c>
+      <c r="J41" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42">
+        <v>666</v>
+      </c>
+      <c r="E42">
+        <v>24</v>
+      </c>
+      <c r="G42">
+        <v>749.62</v>
+      </c>
+      <c r="H42">
+        <v>35524.62</v>
+      </c>
+      <c r="I42" t="s">
+        <v>73</v>
+      </c>
+      <c r="J42" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" t="s">
+        <v>58</v>
+      </c>
+      <c r="D43">
+        <v>666</v>
+      </c>
+      <c r="E43">
+        <v>31</v>
+      </c>
+      <c r="G43">
+        <v>254</v>
+      </c>
+      <c r="H43">
+        <v>35778.62</v>
+      </c>
+      <c r="I43" t="s">
+        <v>73</v>
+      </c>
+      <c r="J43" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44">
+        <v>709</v>
+      </c>
+      <c r="E44">
+        <v>29</v>
+      </c>
+      <c r="G44">
+        <v>808</v>
+      </c>
+      <c r="H44">
+        <v>36586.62</v>
+      </c>
+      <c r="I44" t="s">
+        <v>73</v>
+      </c>
+      <c r="J44" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B45" t="s">
+        <v>60</v>
+      </c>
+      <c r="D45">
+        <v>668</v>
+      </c>
+      <c r="E45">
         <v>18</v>
       </c>
-      <c r="B37" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37">
-        <v>451</v>
-      </c>
-      <c r="E37">
-        <v>11</v>
-      </c>
-      <c r="F37">
-        <v>100</v>
-      </c>
-      <c r="H37">
-        <v>2296</v>
-      </c>
-      <c r="I37" t="s">
-        <v>38</v>
-      </c>
-      <c r="J37" t="s">
-        <v>39</v>
+      <c r="G45">
+        <v>510</v>
+      </c>
+      <c r="H45">
+        <v>37096.62</v>
+      </c>
+      <c r="I45" t="s">
+        <v>73</v>
+      </c>
+      <c r="J45" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46" t="s">
+        <v>61</v>
+      </c>
+      <c r="D46">
+        <v>668</v>
+      </c>
+      <c r="E46">
+        <v>23</v>
+      </c>
+      <c r="G46">
+        <v>284</v>
+      </c>
+      <c r="H46">
+        <v>37380.62</v>
+      </c>
+      <c r="I46" t="s">
+        <v>73</v>
+      </c>
+      <c r="J46" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47" t="s">
+        <v>62</v>
+      </c>
+      <c r="D47">
+        <v>710</v>
+      </c>
+      <c r="E47">
+        <v>22</v>
+      </c>
+      <c r="G47">
+        <v>408</v>
+      </c>
+      <c r="H47">
+        <v>37788.62</v>
+      </c>
+      <c r="I47" t="s">
+        <v>73</v>
+      </c>
+      <c r="J47" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" t="s">
+        <v>63</v>
+      </c>
+      <c r="D48">
+        <v>763</v>
+      </c>
+      <c r="E48">
+        <v>9</v>
+      </c>
+      <c r="G48">
+        <v>204</v>
+      </c>
+      <c r="H48">
+        <v>37992.62</v>
+      </c>
+      <c r="I48" t="s">
+        <v>73</v>
+      </c>
+      <c r="J48" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49" t="s">
+        <v>64</v>
+      </c>
+      <c r="D49">
+        <v>763</v>
+      </c>
+      <c r="E49">
+        <v>10</v>
+      </c>
+      <c r="G49">
+        <v>204</v>
+      </c>
+      <c r="H49">
+        <v>38196.62</v>
+      </c>
+      <c r="I49" t="s">
+        <v>73</v>
+      </c>
+      <c r="J49" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" t="s">
+        <v>65</v>
+      </c>
+      <c r="D50">
+        <v>705</v>
+      </c>
+      <c r="E50">
+        <v>15</v>
+      </c>
+      <c r="G50">
+        <v>479.25</v>
+      </c>
+      <c r="H50">
+        <v>38675.87</v>
+      </c>
+      <c r="I50" t="s">
+        <v>73</v>
+      </c>
+      <c r="J50" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>66</v>
+      </c>
+      <c r="D51">
+        <v>707</v>
+      </c>
+      <c r="E51">
+        <v>24</v>
+      </c>
+      <c r="G51">
+        <v>367</v>
+      </c>
+      <c r="H51">
+        <v>39042.87</v>
+      </c>
+      <c r="I51" t="s">
+        <v>73</v>
+      </c>
+      <c r="J51" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>67</v>
+      </c>
+      <c r="D52">
+        <v>714</v>
+      </c>
+      <c r="E52">
+        <v>25</v>
+      </c>
+      <c r="G52">
+        <v>1387</v>
+      </c>
+      <c r="H52">
+        <v>40429.87</v>
+      </c>
+      <c r="I52" t="s">
+        <v>73</v>
+      </c>
+      <c r="J52" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53">
+        <v>715</v>
+      </c>
+      <c r="E53">
+        <v>93</v>
+      </c>
+      <c r="G53">
+        <v>5018</v>
+      </c>
+      <c r="H53">
+        <v>45447.87</v>
+      </c>
+      <c r="I53" t="s">
+        <v>73</v>
+      </c>
+      <c r="J53" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>69</v>
+      </c>
+      <c r="D54">
+        <v>715</v>
+      </c>
+      <c r="E54">
+        <v>102</v>
+      </c>
+      <c r="G54">
+        <v>840.5</v>
+      </c>
+      <c r="H54">
+        <v>46288.37</v>
+      </c>
+      <c r="I54" t="s">
+        <v>73</v>
+      </c>
+      <c r="J54" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>70</v>
+      </c>
+      <c r="D55">
+        <v>715</v>
+      </c>
+      <c r="E55">
+        <v>189</v>
+      </c>
+      <c r="G55">
+        <v>3534</v>
+      </c>
+      <c r="H55">
+        <v>49822.37</v>
+      </c>
+      <c r="I55" t="s">
+        <v>73</v>
+      </c>
+      <c r="J55" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>71</v>
+      </c>
+      <c r="D56">
+        <v>782</v>
+      </c>
+      <c r="E56">
+        <v>28</v>
+      </c>
+      <c r="G56">
+        <v>153</v>
+      </c>
+      <c r="H56">
+        <v>49975.37</v>
+      </c>
+      <c r="I56" t="s">
+        <v>73</v>
+      </c>
+      <c r="J56" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>72</v>
+      </c>
+      <c r="D57">
+        <v>782</v>
+      </c>
+      <c r="E57">
+        <v>29</v>
+      </c>
+      <c r="G57">
+        <v>153</v>
+      </c>
+      <c r="H57">
+        <v>50128.37</v>
+      </c>
+      <c r="I57" t="s">
+        <v>73</v>
+      </c>
+      <c r="J57" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/processed_file.xlsx
+++ b/processed_file.xlsx
@@ -14,231 +14,324 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="75">
-  <si>
-    <t>2025-01-16</t>
-  </si>
-  <si>
-    <t>2025-01-22</t>
-  </si>
-  <si>
-    <t>2025-01-30</t>
-  </si>
-  <si>
-    <t>2025-01-31</t>
-  </si>
-  <si>
-    <t>2025-02-03</t>
-  </si>
-  <si>
-    <t>2025-02-04</t>
-  </si>
-  <si>
-    <t>2025-02-05</t>
-  </si>
-  <si>
-    <t>2025-02-06</t>
-  </si>
-  <si>
-    <t>2025-02-07</t>
-  </si>
-  <si>
-    <t>2025-02-08</t>
-  </si>
-  <si>
-    <t>2025-02-10</t>
-  </si>
-  <si>
-    <t>2025-02-11</t>
-  </si>
-  <si>
-    <t>2025-02-12</t>
-  </si>
-  <si>
-    <t>2025-02-13</t>
-  </si>
-  <si>
-    <t>2025-02-14</t>
-  </si>
-  <si>
-    <t>2025-02-17</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3061614/3061613</t>
-  </si>
-  <si>
-    <t>N/PGTO. REF. DEVOLUÇÃO D.A. 3146336 B-5940 5 AUGUSTO TORMENA MOREIRA (MARCOS DE OLIVEIRA MOREIRA)</t>
-  </si>
-  <si>
-    <t>N/PGTO. REF. DEVOLUÇÃO D.A. 3147126 B-4669 0 FRANCISCO M DE PAULA XAVIER</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3046187</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3060707</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS VINDI/GALAX D.A. 3061448/3061117/3060824/3046921/3046491</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS VINDI/GALAX D.A. 3063473</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3152390</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152598/3152599/3152947</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152774/3152694</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152093/3152177</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3152317/3152740/3153061</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3152497/3152920/3152292</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3151937</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3154143/3152823</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3060523/3153112/3153308</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3152551/3151823</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152845</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152827</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3153030</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3154236</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3046434</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3151858</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152676/3152677</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3151789/3151778/3153106/3151819/3151790</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3046579</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152541</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3152461/3153143/3152409/3152993/3153093/3152809/3152862</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152558</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152524</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152641</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152884</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3151850/3151851/3151860/3151868/3151899/3151902/3151903/31 51971/3151989/3152008/3152054/3152059/3152191/3152199/3152 204/3152214/3152245/3152263/3152355/3152428/3152531/315253 5/3152539/3152573</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3152585/3152600/3152613/3152620/3152626/3152627/3152630/31 52631/3152633/3152634/3152642/3152654/3152680/3152691/3152 697/3152717/3152729/3152737/3152825/3152831/3152832/315284 9/3152850/3152851</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3152853/3152857/3152865/3152866/3152870/3152871/3152898/31 52907/3152908/3152918/3152936/3152946/3152954/3152960/3153 097/3153120/3155141</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3152358/3152382</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3151856/3152965/3152782/3061588/3152089/3152889/3151834/31 52388/3151835/3151855/3153130/3152888/3151930/3047253/3152 964</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3152151</t>
-  </si>
-  <si>
-    <t>VLR. RECEBIDO D.A. 3152180</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3153302</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152602</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3151996/3152608/3155361/3155415</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3152277</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3061774/3152287/3155350/3152751</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3152061/3155138/3155447</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3144244/3152128</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3152738/3152756</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152372</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3152321</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3153160/3156088</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3152344</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS PIX D.A. 3152858/3152725/3152812/3152778/3152308/3152251</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS VINDI/GALAX D.A. 3152259/3152202/3152750/3152068/3152952/3152216/3152912/31 52078/3152720/3152727/3152726/3152785/3155517/3155371/3151 876/3152923/3151770/3152743/3046199/3152742</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS VINDI/GALAX D.A. 3155673/3152479/3152230/3152268</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS VINDI/GALAX D.A. 3152526/3152057/3153084/3152728/3152596/3152442/3046266/31 52961/3152902/3152478/3152667/3152874/3152628/3151911/31521 54</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3155152</t>
-  </si>
-  <si>
-    <t>VLR. REC. MENSALIDADES/OUTROS CARTÕES CIELO/REDE CAIXA D.A. 3155153</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="106">
+  <si>
+    <t>2025-05-02</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>2025-05-06</t>
+  </si>
+  <si>
+    <t>2025-05-07</t>
+  </si>
+  <si>
+    <t>2025-05-08</t>
+  </si>
+  <si>
+    <t>2025-05-09</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>2025-05-13</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>2025-05-16</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>2025-05-21</t>
+  </si>
+  <si>
+    <t>2025-05-22</t>
+  </si>
+  <si>
+    <t>2025-05-23</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>2025-05-27</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3169607 C-0756 7 ANDREA OLIVEIRA GEBERT</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3116553 C-07656 7 ANDREIA OLIVEIRA GEBERT - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. TRANSFERIDO DA CONTA 4426 P/ 621, REF. VLR. D.A. 3161765 DEVOLVIDO PELA CAMILE PRA SER DESC. DA  SV. 9335 (ANT. TENIS INFANTO SV. 9327)</t>
+  </si>
+  <si>
+    <t>VLR. TRANSFERIDO DA CONTA 4426 P/ 621, REF. VLR. D.A. 3162015 - DEVOLVIDO PELA CAMILE PRA SER DESC. DA  SV. 9335</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3173281 C-00915-5  CAROLINA ALISSA HACKMANN KL - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3174754 C-05643-1 THAYNNA DE MELO BATISTA BUF - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3163387 B-02316-4 RODRIGO GULIN TEIXEIRA DE FA - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. JUROS MENSALIDADES/OUTROS BRADESCO D.A. 3087093 B-05398-0 MARCELO LUIZ BENDHACK - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3087094 B-05398-0 MARCELO LUIZ BENDHACK - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3160662 B-05398-0 MARCELO LUIZ BENDHACK - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3169770 B-05398-0 MARCELO LUIZ BENDHACK - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3110576 C-05292-3 PATRICIA OSTERNAK DE CASTRO - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>N/PGTO. D.A. 3174723 C-06545-1 PATRICIA HELENA DAHER LOPES</t>
+  </si>
+  <si>
+    <t>N/PGTO. D.A. 3174358 B-03709-3 EVELY MARIA ROCHA GOMEZ</t>
+  </si>
+  <si>
+    <t>N/PGTO. D.A. 3174724 C-06545-1 ALESSANDRO PANASOLO</t>
+  </si>
+  <si>
+    <t>N/PGTO. D.A. 3170090 B-3661 0 JOSE CARLOS CASSOU -3153630</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3097606 C-01389-0  FABIO SCARPIM RAMON - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3173443 R-04117-8 VALDIR LIMA CARREIRO - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>N/PGTO. D.A. 3178083/3178081/3178079/3178078 B-5398 MARCELO LUIZ BENDHACK</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3082091 B-04299-9 RAFAEL GAPSKI MOREIRA - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3122904 S-00368-2  HENRIQUE VAROTTO SCOTTI - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR.  REF. REEMBOLSO DE DEPOSITO FEITO POR ENGANO PARA O CLUBE EM 04/05 - MARCELO</t>
+  </si>
+  <si>
+    <t>N/PGTO. D.A. 3178082 B-02316-4 RODRIGO GULIN TEIXEIRA DE F.</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3176111 B-01671-2 ANA AMELIA SOARES ASSAD BRU - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3169627 B 09999-8  PAULO DA NOBREGA SANFORD - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>N/PGTO. REF. DEVOLUÇÃO D.A. 3147480 C-03333-0 CAROLINE CAVASSIN KLAMAS</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3176314 B-01260-8 DANILO PEREIRA NETTO - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. B- 02949-6 FERNANDA ABREU ANDRZEJEWSKI</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. R- 04950-7 0 COSTANTINO ROBERTO COSTANTINI</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3177557 B-00140-2 PETRA KELLER MARSILI - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3169328 B-00373-0 LEANDRO IMTHON ZWEIFEL - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3173991 B-00612-8 ANTONIO PEDRO GASPARIN NET - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3174207 B-00612-8 MARIA DOLORES A DE M GASPAR - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3070385 B-01506-4 -0 MARINA MICHEL DE MACEDO MA -DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3178236 B-02024-7 MARCOS ESPEDITO CARVALHO - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3080308 B-03854-2 MYONG JAE HAN - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3178201 B-04857-1  ILIANE GULLICH MELLUSO - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3087204 B-05415-1  FABIOLA PARIGOT DE SOUZA AZ - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3094857 C-00681-4 FRANCISCO MIN SUK HAN - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3097450 C-01344-4 LUIS AFONSO MACIEL GUGELMIN - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3101476 C-02375-6 INACIO LEE SUK HAN - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3109868 C-04948-6 GREGORIO WUN SUK HAN - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3114386 C-06908-3 CRISTINE OSTERNACK COSTA - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3115469 C-07284-5 DANIEL MAZER DE ARAUJO - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3131606 R-03323-5 GLAUCIO LUIZ BACHMANN ALVES - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3122469 S-00295-6 BRUNA MICHALCZUK CICHON - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3175771 B-05474-2 THIAGO VON DER OSTEN CRAVO - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3176895 B-06272-7 GRAZIELA BEDUSCHI - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3175177 b- 09999-8 PAULO DA NOBREGA SANFORD - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3106837 C-04050-4 MONICA HAE JO HAN - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. R- 04947-1 0 ANTENOR RIBEIRO BONFIM</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3171209 R-03672-3 SERGIO AUGUSTO DE MUNHOZ P - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>N/PGTO. REF. DEVOLUÇÃO D.A. 3178797  MARCELO APARECIDO SARAIVA - REFERENTE DEPÓSITO RECEBIDO NO BANCO ITAU FEITO INDEVIDAMENTE PELO REMETENTE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS VINDI/GALAX D.A. 3176451 B-3121 ROGERIO PINTO MUNIZ FILHO - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3071458 B-01755-9 MARCELLO LUPARIA - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3177739 B-02152-3 MARCELO GERALDI VELLOSO - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3172057 R-04302-3 NEUZA NOGUCHI MACHUCA - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>N/PGTO. REF. DEVOLUÇÃO D.A. 3179329  B-02949-6 FERNANDA ABREU ANDRZEJEWSKI</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3175260 C-08274-3 MATHEUS CHEMIM LORENCI - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3089061 B-05754-4 JULIANA LEME BRAZ MENDONCA - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3125015 S-00836-6 GABRIEL BRAZ MENDONCA - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>N/PGTO. D.A. 3179915 B-05754-4 JULIANA LEME BRAZ MENDONCA</t>
+  </si>
+  <si>
+    <t>N/PGTO. D.A. 3179916 S-00836-6 GABRIEL BRAZ MENDONCA</t>
+  </si>
+  <si>
+    <t>VLR. RECEBIDO D.A. 3172463 B-00447 1 CAMILA FERREIRA DA COSTA TEIXEIRA</t>
+  </si>
+  <si>
+    <t>N/PGTO. REF. DEVOLUÇÃO D.A. 3179516 C-03333-0 CAROLINE CAVASSIN KLAMAS</t>
+  </si>
+  <si>
+    <t>N/PGTO. D.A. 3155551 B-00910 8 MARISA VIEIRA FREDERICO DE MIO</t>
+  </si>
+  <si>
+    <t>N/PGTO. D.A. 3155550 B-00910 8 MARISA VIEIRA FREDERICO DE MIO</t>
+  </si>
+  <si>
+    <t>N/PGTO. D.A. 3064066 B-910 8 OLIVIA FREDERICO DE MIO</t>
+  </si>
+  <si>
+    <t>N/PGTO. D.A. 3064068 B-00910 8 MARISA VIEIRA FREDERICO DE MIO</t>
+  </si>
+  <si>
+    <t>N/PGTO. D.A. 3178485 C-01389 0 FABIO SCARPIM RAMON</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3179107 B-05777-0  ALICIA CAVALINI SOARES - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. RECEBIDO D.A. 3179217 C-01344 4 LUIS AFONSO MACIEL GUGELMIM</t>
+  </si>
+  <si>
+    <t>N/PGTO. D.A. 3179377 R-03672-3 -0 SERGIO AUGUSTO DE MUNHOZ</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3169344 C-06692-1 -0 CAROLINA FERES BUSATO - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3090912 B-06066-7 -0 FELIPE AUGUSTO HOFFMANN CO - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>PAGAMENTOS N/DATA 3179220 C-04948-6 GREGORIO WUN SUK HAN</t>
+  </si>
+  <si>
+    <t>PAGAMENTOS N/DATA 3172916 C-00681 4 FRANCISCO MIN SUK HAN</t>
+  </si>
+  <si>
+    <t>PAGAMENTOS N/DATA 3179219 C-04050-4 MONICA HAE JO HAN</t>
+  </si>
+  <si>
+    <t>PAGAMENTOS N/DATA 3179218 C-02375-6 INACIO LEE SUK HAN</t>
+  </si>
+  <si>
+    <t>VLR. RECEBIDO D.A. 3177375 C-07656 7 ANDREA OLIVEIRA GEBERT</t>
+  </si>
+  <si>
+    <t>N/PGTO. REF. DEVOLUÇÃO D.A. 3177376 C-7656 0 ANDREA OLIVEIRA GEBERT</t>
+  </si>
+  <si>
+    <t>N/PGTO. REF. DEVOLUÇÃO D.A. 3179227/3179226  B-612 ANTONIO PEDRO GASPARIN NET</t>
+  </si>
+  <si>
+    <t>VLR. REC. MENSALIDADES/OUTROS BRADESCO D.A. 3172470 C-03661-3 ALEXANDRE BRAMBILLA KRAUSE - DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>N/PGTO. REF. DEVOLUÇÃO D.A. 3179214 B-3854 MYONG JAE HAN</t>
   </si>
   <si>
     <t>C</t>
   </si>
   <si>
-    <t>22176</t>
+    <t>04426</t>
   </si>
 </sst>
 </file>
@@ -570,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -578,25 +671,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D1">
-        <v>223</v>
+        <v>2366</v>
       </c>
       <c r="E1">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="G1">
-        <v>548</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="H1">
-        <v>4429.63</v>
+        <v>63709.47</v>
       </c>
       <c r="I1" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J1" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -604,1455 +697,2189 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>241</v>
+        <v>2366</v>
       </c>
       <c r="E2">
-        <v>35</v>
-      </c>
-      <c r="F2">
-        <v>102</v>
+        <v>22</v>
+      </c>
+      <c r="G2">
+        <v>784.28</v>
       </c>
       <c r="H2">
-        <v>4327.63</v>
+        <v>64493.75</v>
       </c>
       <c r="I2" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J2" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="C3">
+        <v>621</v>
       </c>
       <c r="D3">
-        <v>372</v>
+        <v>2452</v>
       </c>
       <c r="E3">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F3">
-        <v>83.63</v>
+        <v>51.85</v>
       </c>
       <c r="H3">
-        <v>4244</v>
+        <v>64441.9</v>
       </c>
       <c r="I3" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J3" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>23</v>
+      </c>
+      <c r="C4">
+        <v>621</v>
       </c>
       <c r="D4">
-        <v>467</v>
+        <v>2452</v>
       </c>
       <c r="E4">
-        <v>17</v>
-      </c>
-      <c r="G4">
-        <v>196</v>
+        <v>44</v>
+      </c>
+      <c r="F4">
+        <v>6.92</v>
       </c>
       <c r="H4">
-        <v>4440</v>
+        <v>64434.98</v>
       </c>
       <c r="I4" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J4" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D5">
-        <v>478</v>
+        <v>2469</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>196</v>
+        <v>93</v>
       </c>
       <c r="H5">
-        <v>4636</v>
+        <v>64527.98</v>
       </c>
       <c r="I5" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J5" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D6">
-        <v>502</v>
+        <v>2469</v>
       </c>
       <c r="E6">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>980</v>
+        <v>156</v>
       </c>
       <c r="H6">
-        <v>5616</v>
+        <v>64683.98</v>
       </c>
       <c r="I6" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J6" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D7">
-        <v>502</v>
+        <v>2471</v>
       </c>
       <c r="E7">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="G7">
-        <v>34</v>
+        <v>99.39</v>
       </c>
       <c r="H7">
-        <v>5650</v>
+        <v>64783.37</v>
       </c>
       <c r="I7" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J7" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D8">
-        <v>480</v>
+        <v>2471</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="G8">
-        <v>204</v>
+        <v>793.28</v>
       </c>
       <c r="H8">
-        <v>5854</v>
+        <v>65576.64999999999</v>
       </c>
       <c r="I8" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J8" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D9">
-        <v>509</v>
+        <v>2471</v>
       </c>
       <c r="E9">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="G9">
-        <v>612</v>
+        <v>785.53</v>
       </c>
       <c r="H9">
-        <v>6466</v>
+        <v>66362.17999999999</v>
       </c>
       <c r="I9" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J9" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D10">
-        <v>512</v>
+        <v>2471</v>
       </c>
       <c r="E10">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="G10">
-        <v>571</v>
+        <v>155.8</v>
       </c>
       <c r="H10">
-        <v>7037</v>
+        <v>66517.98</v>
       </c>
       <c r="I10" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J10" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D11">
-        <v>512</v>
+        <v>2471</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="G11">
-        <v>396</v>
+        <v>154.25</v>
       </c>
       <c r="H11">
-        <v>7433</v>
+        <v>66672.23</v>
       </c>
       <c r="I11" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J11" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D12">
-        <v>619</v>
+        <v>2471</v>
       </c>
       <c r="E12">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G12">
-        <v>612</v>
+        <v>785.53</v>
       </c>
       <c r="H12">
-        <v>8045</v>
+        <v>67457.75999999999</v>
       </c>
       <c r="I12" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J12" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D13">
-        <v>637</v>
+        <v>2607</v>
       </c>
       <c r="E13">
-        <v>24</v>
-      </c>
-      <c r="G13">
-        <v>612</v>
+        <v>37</v>
+      </c>
+      <c r="F13">
+        <v>791.53</v>
       </c>
       <c r="H13">
-        <v>8657</v>
+        <v>66666.23</v>
       </c>
       <c r="I13" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J13" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D14">
-        <v>720</v>
+        <v>2607</v>
       </c>
       <c r="E14">
-        <v>48</v>
-      </c>
-      <c r="G14">
-        <v>204</v>
+        <v>40</v>
+      </c>
+      <c r="F14">
+        <v>80</v>
       </c>
       <c r="H14">
-        <v>8861</v>
+        <v>66586.23</v>
       </c>
       <c r="I14" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J14" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D15">
-        <v>721</v>
+        <v>2607</v>
       </c>
       <c r="E15">
-        <v>15</v>
-      </c>
-      <c r="G15">
-        <v>408</v>
+        <v>41</v>
+      </c>
+      <c r="F15">
+        <v>526.83</v>
       </c>
       <c r="H15">
-        <v>9269</v>
+        <v>66059.39999999999</v>
       </c>
       <c r="I15" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J15" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D16">
-        <v>621</v>
+        <v>2461</v>
       </c>
       <c r="E16">
-        <v>27</v>
-      </c>
-      <c r="G16">
-        <v>767</v>
+        <v>22</v>
+      </c>
+      <c r="F16">
+        <v>125.5</v>
       </c>
       <c r="H16">
-        <v>10036</v>
+        <v>65933.89999999999</v>
       </c>
       <c r="I16" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J16" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D17">
-        <v>638</v>
+        <v>2473</v>
       </c>
       <c r="E17">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="G17">
-        <v>408</v>
+        <v>785.78</v>
       </c>
       <c r="H17">
-        <v>10444</v>
+        <v>66719.67999999999</v>
       </c>
       <c r="I17" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J17" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D18">
-        <v>724</v>
+        <v>2473</v>
       </c>
       <c r="E18">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="G18">
-        <v>204</v>
+        <v>80</v>
       </c>
       <c r="H18">
-        <v>10648</v>
+        <v>66799.67999999999</v>
       </c>
       <c r="I18" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J18" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D19">
-        <v>725</v>
+        <v>2611</v>
       </c>
       <c r="E19">
-        <v>29</v>
-      </c>
-      <c r="G19">
-        <v>204</v>
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>1888.86</v>
       </c>
       <c r="H19">
-        <v>10852</v>
+        <v>64910.82</v>
       </c>
       <c r="I19" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J19" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D20">
-        <v>725</v>
+        <v>2475</v>
       </c>
       <c r="E20">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G20">
-        <v>204</v>
+        <v>764</v>
       </c>
       <c r="H20">
-        <v>11056</v>
+        <v>65674.82000000001</v>
       </c>
       <c r="I20" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J20" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D21">
-        <v>623</v>
+        <v>2475</v>
       </c>
       <c r="E21">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G21">
-        <v>153</v>
+        <v>382</v>
       </c>
       <c r="H21">
-        <v>11209</v>
+        <v>66056.82000000001</v>
       </c>
       <c r="I21" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J21" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D22">
-        <v>677</v>
+        <v>2494</v>
       </c>
       <c r="E22">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G22">
-        <v>196</v>
+        <v>50</v>
       </c>
       <c r="H22">
-        <v>11405</v>
+        <v>66106.82000000001</v>
       </c>
       <c r="I22" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J22" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D23">
-        <v>730</v>
+        <v>2612</v>
       </c>
       <c r="E23">
-        <v>13</v>
-      </c>
-      <c r="G23">
-        <v>204</v>
+        <v>37</v>
+      </c>
+      <c r="F23">
+        <v>99.39</v>
       </c>
       <c r="H23">
-        <v>11609</v>
+        <v>66007.42999999999</v>
       </c>
       <c r="I23" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J23" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D24">
-        <v>732</v>
+        <v>2490</v>
       </c>
       <c r="E24">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G24">
-        <v>408</v>
+        <v>305</v>
       </c>
       <c r="H24">
-        <v>12017</v>
+        <v>66312.42999999999</v>
       </c>
       <c r="I24" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J24" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D25">
-        <v>639</v>
+        <v>2490</v>
       </c>
       <c r="E25">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G25">
-        <v>1020</v>
+        <v>310.84</v>
       </c>
       <c r="H25">
-        <v>13037</v>
+        <v>66623.27</v>
       </c>
       <c r="I25" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J25" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D26">
-        <v>735</v>
+        <v>2588</v>
       </c>
       <c r="E26">
-        <v>25</v>
-      </c>
-      <c r="G26">
-        <v>196</v>
+        <v>47</v>
+      </c>
+      <c r="F26">
+        <v>191</v>
       </c>
       <c r="H26">
-        <v>13233</v>
+        <v>66432.27</v>
       </c>
       <c r="I26" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J26" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D27">
-        <v>741</v>
+        <v>2548</v>
       </c>
       <c r="E27">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="G27">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="H27">
-        <v>13437</v>
+        <v>66618.27</v>
       </c>
       <c r="I27" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J27" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D28">
-        <v>640</v>
+        <v>2655</v>
       </c>
       <c r="E28">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="G28">
-        <v>1591</v>
+        <v>764</v>
       </c>
       <c r="H28">
-        <v>15028</v>
+        <v>67382.27</v>
       </c>
       <c r="I28" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J28" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D29">
-        <v>744</v>
+        <v>2655</v>
       </c>
       <c r="E29">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G29">
-        <v>204</v>
+        <v>764</v>
       </c>
       <c r="H29">
-        <v>15232</v>
+        <v>68146.27</v>
       </c>
       <c r="I29" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J29" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D30">
-        <v>744</v>
+        <v>2552</v>
       </c>
       <c r="E30">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G30">
-        <v>204</v>
+        <v>34</v>
       </c>
       <c r="H30">
-        <v>15436</v>
+        <v>68180.27</v>
       </c>
       <c r="I30" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J30" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D31">
-        <v>748</v>
+        <v>2553</v>
       </c>
       <c r="E31">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="G31">
-        <v>204</v>
+        <v>135.92</v>
       </c>
       <c r="H31">
-        <v>15640</v>
+        <v>68316.19</v>
       </c>
       <c r="I31" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J31" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D32">
-        <v>748</v>
+        <v>2553</v>
       </c>
       <c r="E32">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="G32">
-        <v>204</v>
+        <v>80</v>
       </c>
       <c r="H32">
-        <v>15844</v>
+        <v>68396.19</v>
       </c>
       <c r="I32" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J32" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D33">
-        <v>629</v>
+        <v>2553</v>
       </c>
       <c r="E33">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="G33">
-        <v>5711</v>
+        <v>80</v>
       </c>
       <c r="H33">
-        <v>21555</v>
+        <v>68476.19</v>
       </c>
       <c r="I33" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J33" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D34">
-        <v>629</v>
+        <v>2553</v>
       </c>
       <c r="E34">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="G34">
-        <v>5222</v>
+        <v>764</v>
       </c>
       <c r="H34">
-        <v>26777</v>
+        <v>69240.19</v>
       </c>
       <c r="I34" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J34" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D35">
-        <v>629</v>
+        <v>2553</v>
       </c>
       <c r="E35">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="G35">
-        <v>3417</v>
+        <v>676</v>
       </c>
       <c r="H35">
-        <v>30194</v>
+        <v>69916.19</v>
       </c>
       <c r="I35" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J35" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D36">
-        <v>629</v>
+        <v>2553</v>
       </c>
       <c r="E36">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="G36">
-        <v>508</v>
+        <v>764</v>
       </c>
       <c r="H36">
-        <v>30702</v>
+        <v>70680.19</v>
       </c>
       <c r="I36" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J36" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D37">
-        <v>641</v>
+        <v>2553</v>
       </c>
       <c r="E37">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="G37">
-        <v>3207</v>
+        <v>711</v>
       </c>
       <c r="H37">
-        <v>33909</v>
+        <v>71391.19</v>
       </c>
       <c r="I37" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J37" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D38">
-        <v>641</v>
+        <v>2553</v>
       </c>
       <c r="E38">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="G38">
-        <v>254</v>
+        <v>764</v>
       </c>
       <c r="H38">
-        <v>34163</v>
+        <v>72155.19</v>
       </c>
       <c r="I38" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J38" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D39">
-        <v>750</v>
+        <v>2553</v>
       </c>
       <c r="E39">
-        <v>9</v>
+        <v>101</v>
       </c>
       <c r="G39">
-        <v>204</v>
+        <v>764</v>
       </c>
       <c r="H39">
-        <v>34367</v>
+        <v>72919.19</v>
       </c>
       <c r="I39" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J39" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B40" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D40">
-        <v>750</v>
+        <v>2553</v>
       </c>
       <c r="E40">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="G40">
-        <v>204</v>
+        <v>764</v>
       </c>
       <c r="H40">
-        <v>34571</v>
+        <v>73683.19</v>
       </c>
       <c r="I40" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J40" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D41">
-        <v>753</v>
+        <v>2553</v>
       </c>
       <c r="E41">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="G41">
-        <v>204</v>
+        <v>764</v>
       </c>
       <c r="H41">
-        <v>34775</v>
+        <v>74447.19</v>
       </c>
       <c r="I41" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J41" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D42">
-        <v>666</v>
+        <v>2553</v>
       </c>
       <c r="E42">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="G42">
-        <v>749.62</v>
+        <v>764</v>
       </c>
       <c r="H42">
-        <v>35524.62</v>
+        <v>75211.19</v>
       </c>
       <c r="I42" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J42" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D43">
-        <v>666</v>
+        <v>2553</v>
       </c>
       <c r="E43">
-        <v>31</v>
+        <v>105</v>
       </c>
       <c r="G43">
-        <v>254</v>
+        <v>764</v>
       </c>
       <c r="H43">
-        <v>35778.62</v>
+        <v>75975.19</v>
       </c>
       <c r="I43" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J43" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D44">
-        <v>709</v>
+        <v>2553</v>
       </c>
       <c r="E44">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="G44">
-        <v>808</v>
+        <v>764</v>
       </c>
       <c r="H44">
-        <v>36586.62</v>
+        <v>76739.19</v>
       </c>
       <c r="I44" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J44" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D45">
-        <v>668</v>
+        <v>2553</v>
       </c>
       <c r="E45">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="G45">
-        <v>510</v>
+        <v>382</v>
       </c>
       <c r="H45">
-        <v>37096.62</v>
+        <v>77121.19</v>
       </c>
       <c r="I45" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J45" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D46">
-        <v>668</v>
+        <v>2553</v>
       </c>
       <c r="E46">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="G46">
-        <v>284</v>
+        <v>393.8</v>
       </c>
       <c r="H46">
-        <v>37380.62</v>
+        <v>77514.99000000001</v>
       </c>
       <c r="I46" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J46" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D47">
-        <v>710</v>
+        <v>2553</v>
       </c>
       <c r="E47">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="G47">
-        <v>408</v>
+        <v>366</v>
       </c>
       <c r="H47">
-        <v>37788.62</v>
+        <v>77880.99000000001</v>
       </c>
       <c r="I47" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J47" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D48">
-        <v>763</v>
+        <v>2553</v>
       </c>
       <c r="E48">
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="G48">
         <v>204</v>
       </c>
       <c r="H48">
-        <v>37992.62</v>
+        <v>78084.99000000001</v>
       </c>
       <c r="I48" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J48" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B49" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D49">
-        <v>763</v>
+        <v>2553</v>
       </c>
       <c r="E49">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="G49">
-        <v>204</v>
+        <v>302</v>
       </c>
       <c r="H49">
-        <v>38196.62</v>
+        <v>78386.99000000001</v>
       </c>
       <c r="I49" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J49" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B50" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D50">
-        <v>705</v>
+        <v>2553</v>
       </c>
       <c r="E50">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="G50">
-        <v>479.25</v>
+        <v>764</v>
       </c>
       <c r="H50">
-        <v>38675.87</v>
+        <v>79150.99000000001</v>
       </c>
       <c r="I50" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J50" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D51">
-        <v>707</v>
+        <v>2658</v>
       </c>
       <c r="E51">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G51">
-        <v>367</v>
+        <v>764</v>
       </c>
       <c r="H51">
-        <v>39042.87</v>
+        <v>79914.99000000001</v>
       </c>
       <c r="I51" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J51" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B52" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D52">
-        <v>714</v>
+        <v>2623</v>
       </c>
       <c r="E52">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="G52">
-        <v>1387</v>
+        <v>382</v>
       </c>
       <c r="H52">
-        <v>40429.87</v>
+        <v>80296.99000000001</v>
       </c>
       <c r="I52" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J52" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D53">
-        <v>715</v>
+        <v>2660</v>
       </c>
       <c r="E53">
-        <v>93</v>
-      </c>
-      <c r="G53">
-        <v>5018</v>
+        <v>61</v>
+      </c>
+      <c r="F53">
+        <v>50</v>
       </c>
       <c r="H53">
-        <v>45447.87</v>
+        <v>80246.99000000001</v>
       </c>
       <c r="I53" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J53" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D54">
-        <v>715</v>
+        <v>2675</v>
       </c>
       <c r="E54">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="G54">
-        <v>840.5</v>
+        <v>186</v>
       </c>
       <c r="H54">
-        <v>46288.37</v>
+        <v>80432.99000000001</v>
       </c>
       <c r="I54" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J54" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B55" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D55">
-        <v>715</v>
+        <v>2625</v>
       </c>
       <c r="E55">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="G55">
-        <v>3534</v>
+        <v>780.28</v>
       </c>
       <c r="H55">
-        <v>49822.37</v>
+        <v>81213.27</v>
       </c>
       <c r="I55" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J55" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56" t="s">
+        <v>75</v>
+      </c>
+      <c r="D56">
+        <v>2654</v>
+      </c>
+      <c r="E56">
         <v>15</v>
       </c>
-      <c r="B56" t="s">
-        <v>71</v>
-      </c>
-      <c r="D56">
-        <v>782</v>
-      </c>
-      <c r="E56">
-        <v>28</v>
-      </c>
       <c r="G56">
-        <v>153</v>
+        <v>139.5</v>
       </c>
       <c r="H56">
-        <v>49975.37</v>
+        <v>81352.77</v>
       </c>
       <c r="I56" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J56" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" t="s">
+        <v>10</v>
+      </c>
+      <c r="B57" t="s">
+        <v>76</v>
+      </c>
+      <c r="D57">
+        <v>2654</v>
+      </c>
+      <c r="E57">
+        <v>24</v>
+      </c>
+      <c r="G57">
+        <v>50</v>
+      </c>
+      <c r="H57">
+        <v>81402.77</v>
+      </c>
+      <c r="I57" t="s">
+        <v>104</v>
+      </c>
+      <c r="J57" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" t="s">
+        <v>10</v>
+      </c>
+      <c r="B58" t="s">
+        <v>77</v>
+      </c>
+      <c r="D58">
+        <v>2715</v>
+      </c>
+      <c r="E58">
+        <v>59</v>
+      </c>
+      <c r="F58">
+        <v>764</v>
+      </c>
+      <c r="H58">
+        <v>80638.77</v>
+      </c>
+      <c r="I58" t="s">
+        <v>104</v>
+      </c>
+      <c r="J58" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59" t="s">
+        <v>78</v>
+      </c>
+      <c r="D59">
+        <v>2704</v>
+      </c>
+      <c r="E59">
+        <v>7</v>
+      </c>
+      <c r="G59">
+        <v>213.6</v>
+      </c>
+      <c r="H59">
+        <v>80852.37</v>
+      </c>
+      <c r="I59" t="s">
+        <v>104</v>
+      </c>
+      <c r="J59" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" t="s">
+        <v>79</v>
+      </c>
+      <c r="D60">
+        <v>2704</v>
+      </c>
+      <c r="E60">
+        <v>23</v>
+      </c>
+      <c r="G60">
+        <v>780.78</v>
+      </c>
+      <c r="H60">
+        <v>81633.14999999999</v>
+      </c>
+      <c r="I60" t="s">
+        <v>104</v>
+      </c>
+      <c r="J60" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" t="s">
+        <v>11</v>
+      </c>
+      <c r="B61" t="s">
+        <v>80</v>
+      </c>
+      <c r="D61">
+        <v>2704</v>
+      </c>
+      <c r="E61">
+        <v>24</v>
+      </c>
+      <c r="G61">
+        <v>390.42</v>
+      </c>
+      <c r="H61">
+        <v>82023.57000000001</v>
+      </c>
+      <c r="I61" t="s">
+        <v>104</v>
+      </c>
+      <c r="J61" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" t="s">
+        <v>81</v>
+      </c>
+      <c r="D62">
+        <v>2791</v>
+      </c>
+      <c r="E62">
+        <v>20</v>
+      </c>
+      <c r="F62">
+        <v>780.78</v>
+      </c>
+      <c r="H62">
+        <v>81242.78999999999</v>
+      </c>
+      <c r="I62" t="s">
+        <v>104</v>
+      </c>
+      <c r="J62" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" t="s">
+        <v>82</v>
+      </c>
+      <c r="D63">
+        <v>2791</v>
+      </c>
+      <c r="E63">
+        <v>22</v>
+      </c>
+      <c r="F63">
+        <v>390.42</v>
+      </c>
+      <c r="H63">
+        <v>80852.37</v>
+      </c>
+      <c r="I63" t="s">
+        <v>104</v>
+      </c>
+      <c r="J63" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" t="s">
+        <v>12</v>
+      </c>
+      <c r="B64" t="s">
+        <v>83</v>
+      </c>
+      <c r="D64">
+        <v>2820</v>
+      </c>
+      <c r="E64">
+        <v>5</v>
+      </c>
+      <c r="F64">
+        <v>788.28</v>
+      </c>
+      <c r="H64">
+        <v>80064.09</v>
+      </c>
+      <c r="I64" t="s">
+        <v>104</v>
+      </c>
+      <c r="J64" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" t="s">
+        <v>84</v>
+      </c>
+      <c r="D65">
+        <v>2828</v>
+      </c>
+      <c r="E65">
         <v>15</v>
       </c>
-      <c r="B57" t="s">
-        <v>72</v>
-      </c>
-      <c r="D57">
-        <v>782</v>
-      </c>
-      <c r="E57">
-        <v>29</v>
-      </c>
-      <c r="G57">
-        <v>153</v>
-      </c>
-      <c r="H57">
-        <v>50128.37</v>
-      </c>
-      <c r="I57" t="s">
-        <v>73</v>
-      </c>
-      <c r="J57" t="s">
-        <v>74</v>
+      <c r="F65">
+        <v>764</v>
+      </c>
+      <c r="H65">
+        <v>79300.09</v>
+      </c>
+      <c r="I65" t="s">
+        <v>104</v>
+      </c>
+      <c r="J65" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B66" t="s">
+        <v>85</v>
+      </c>
+      <c r="D66">
+        <v>2822</v>
+      </c>
+      <c r="E66">
+        <v>18</v>
+      </c>
+      <c r="F66">
+        <v>186</v>
+      </c>
+      <c r="H66">
+        <v>79114.09</v>
+      </c>
+      <c r="I66" t="s">
+        <v>104</v>
+      </c>
+      <c r="J66" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" t="s">
+        <v>13</v>
+      </c>
+      <c r="B67" t="s">
+        <v>86</v>
+      </c>
+      <c r="D67">
+        <v>2822</v>
+      </c>
+      <c r="E67">
+        <v>19</v>
+      </c>
+      <c r="F67">
+        <v>464</v>
+      </c>
+      <c r="H67">
+        <v>78650.09</v>
+      </c>
+      <c r="I67" t="s">
+        <v>104</v>
+      </c>
+      <c r="J67" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" t="s">
+        <v>13</v>
+      </c>
+      <c r="B68" t="s">
+        <v>87</v>
+      </c>
+      <c r="D68">
+        <v>2822</v>
+      </c>
+      <c r="E68">
+        <v>39</v>
+      </c>
+      <c r="F68">
+        <v>76.95</v>
+      </c>
+      <c r="H68">
+        <v>78573.14</v>
+      </c>
+      <c r="I68" t="s">
+        <v>104</v>
+      </c>
+      <c r="J68" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" t="s">
+        <v>13</v>
+      </c>
+      <c r="B69" t="s">
+        <v>88</v>
+      </c>
+      <c r="D69">
+        <v>2822</v>
+      </c>
+      <c r="E69">
+        <v>75</v>
+      </c>
+      <c r="F69">
+        <v>445</v>
+      </c>
+      <c r="H69">
+        <v>78128.14</v>
+      </c>
+      <c r="I69" t="s">
+        <v>104</v>
+      </c>
+      <c r="J69" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" t="s">
+        <v>13</v>
+      </c>
+      <c r="B70" t="s">
+        <v>85</v>
+      </c>
+      <c r="D70">
+        <v>2822</v>
+      </c>
+      <c r="E70">
+        <v>76</v>
+      </c>
+      <c r="F70">
+        <v>178</v>
+      </c>
+      <c r="H70">
+        <v>77950.14</v>
+      </c>
+      <c r="I70" t="s">
+        <v>104</v>
+      </c>
+      <c r="J70" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" t="s">
+        <v>13</v>
+      </c>
+      <c r="B71" t="s">
+        <v>89</v>
+      </c>
+      <c r="D71">
+        <v>2824</v>
+      </c>
+      <c r="E71">
+        <v>4</v>
+      </c>
+      <c r="F71">
+        <v>785.78</v>
+      </c>
+      <c r="H71">
+        <v>77164.36</v>
+      </c>
+      <c r="I71" t="s">
+        <v>104</v>
+      </c>
+      <c r="J71" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" t="s">
+        <v>14</v>
+      </c>
+      <c r="B72" t="s">
+        <v>90</v>
+      </c>
+      <c r="D72">
+        <v>2847</v>
+      </c>
+      <c r="E72">
+        <v>17</v>
+      </c>
+      <c r="G72">
+        <v>186</v>
+      </c>
+      <c r="H72">
+        <v>77350.36</v>
+      </c>
+      <c r="I72" t="s">
+        <v>104</v>
+      </c>
+      <c r="J72" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" t="s">
+        <v>14</v>
+      </c>
+      <c r="B73" t="s">
+        <v>91</v>
+      </c>
+      <c r="D73">
+        <v>2972</v>
+      </c>
+      <c r="E73">
+        <v>3</v>
+      </c>
+      <c r="F73">
+        <v>764</v>
+      </c>
+      <c r="H73">
+        <v>76586.36</v>
+      </c>
+      <c r="I73" t="s">
+        <v>104</v>
+      </c>
+      <c r="J73" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>92</v>
+      </c>
+      <c r="D74">
+        <v>2881</v>
+      </c>
+      <c r="E74">
+        <v>53</v>
+      </c>
+      <c r="F74">
+        <v>382</v>
+      </c>
+      <c r="H74">
+        <v>76204.36</v>
+      </c>
+      <c r="I74" t="s">
+        <v>104</v>
+      </c>
+      <c r="J74" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" t="s">
+        <v>16</v>
+      </c>
+      <c r="B75" t="s">
+        <v>93</v>
+      </c>
+      <c r="D75">
+        <v>2883</v>
+      </c>
+      <c r="E75">
+        <v>12</v>
+      </c>
+      <c r="G75">
+        <v>194.52</v>
+      </c>
+      <c r="H75">
+        <v>76398.88</v>
+      </c>
+      <c r="I75" t="s">
+        <v>104</v>
+      </c>
+      <c r="J75" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" t="s">
+        <v>16</v>
+      </c>
+      <c r="B76" t="s">
+        <v>94</v>
+      </c>
+      <c r="D76">
+        <v>2883</v>
+      </c>
+      <c r="E76">
+        <v>22</v>
+      </c>
+      <c r="G76">
+        <v>783.28</v>
+      </c>
+      <c r="H76">
+        <v>77182.16</v>
+      </c>
+      <c r="I76" t="s">
+        <v>104</v>
+      </c>
+      <c r="J76" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" t="s">
+        <v>16</v>
+      </c>
+      <c r="B77" t="s">
+        <v>95</v>
+      </c>
+      <c r="D77">
+        <v>2931</v>
+      </c>
+      <c r="E77">
+        <v>4</v>
+      </c>
+      <c r="F77">
+        <v>764</v>
+      </c>
+      <c r="H77">
+        <v>76418.16</v>
+      </c>
+      <c r="I77" t="s">
+        <v>104</v>
+      </c>
+      <c r="J77" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" t="s">
+        <v>16</v>
+      </c>
+      <c r="B78" t="s">
+        <v>96</v>
+      </c>
+      <c r="D78">
+        <v>2931</v>
+      </c>
+      <c r="E78">
+        <v>22</v>
+      </c>
+      <c r="F78">
+        <v>764</v>
+      </c>
+      <c r="H78">
+        <v>75654.16</v>
+      </c>
+      <c r="I78" t="s">
+        <v>104</v>
+      </c>
+      <c r="J78" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" t="s">
+        <v>16</v>
+      </c>
+      <c r="B79" t="s">
+        <v>97</v>
+      </c>
+      <c r="D79">
+        <v>2931</v>
+      </c>
+      <c r="E79">
+        <v>23</v>
+      </c>
+      <c r="F79">
+        <v>764</v>
+      </c>
+      <c r="H79">
+        <v>74890.16</v>
+      </c>
+      <c r="I79" t="s">
+        <v>104</v>
+      </c>
+      <c r="J79" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" t="s">
+        <v>16</v>
+      </c>
+      <c r="B80" t="s">
+        <v>98</v>
+      </c>
+      <c r="D80">
+        <v>2931</v>
+      </c>
+      <c r="E80">
+        <v>24</v>
+      </c>
+      <c r="F80">
+        <v>764</v>
+      </c>
+      <c r="H80">
+        <v>74126.16</v>
+      </c>
+      <c r="I80" t="s">
+        <v>104</v>
+      </c>
+      <c r="J80" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81" t="s">
+        <v>17</v>
+      </c>
+      <c r="B81" t="s">
+        <v>99</v>
+      </c>
+      <c r="D81">
+        <v>2939</v>
+      </c>
+      <c r="E81">
+        <v>2</v>
+      </c>
+      <c r="F81">
+        <v>784.28</v>
+      </c>
+      <c r="H81">
+        <v>73341.88</v>
+      </c>
+      <c r="I81" t="s">
+        <v>104</v>
+      </c>
+      <c r="J81" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" t="s">
+        <v>17</v>
+      </c>
+      <c r="B82" t="s">
+        <v>100</v>
+      </c>
+      <c r="D82">
+        <v>2939</v>
+      </c>
+      <c r="E82">
+        <v>7</v>
+      </c>
+      <c r="F82">
+        <v>88.31999999999999</v>
+      </c>
+      <c r="H82">
+        <v>73253.56</v>
+      </c>
+      <c r="I82" t="s">
+        <v>104</v>
+      </c>
+      <c r="J82" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" t="s">
+        <v>17</v>
+      </c>
+      <c r="B83" t="s">
+        <v>101</v>
+      </c>
+      <c r="D83">
+        <v>2949</v>
+      </c>
+      <c r="E83">
+        <v>13</v>
+      </c>
+      <c r="F83">
+        <v>160</v>
+      </c>
+      <c r="H83">
+        <v>73093.56</v>
+      </c>
+      <c r="I83" t="s">
+        <v>104</v>
+      </c>
+      <c r="J83" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" t="s">
+        <v>18</v>
+      </c>
+      <c r="B84" t="s">
+        <v>102</v>
+      </c>
+      <c r="D84">
+        <v>2916</v>
+      </c>
+      <c r="E84">
+        <v>18</v>
+      </c>
+      <c r="G84">
+        <v>275.94</v>
+      </c>
+      <c r="H84">
+        <v>73369.5</v>
+      </c>
+      <c r="I84" t="s">
+        <v>104</v>
+      </c>
+      <c r="J84" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" t="s">
+        <v>19</v>
+      </c>
+      <c r="B85" t="s">
+        <v>103</v>
+      </c>
+      <c r="D85">
+        <v>3028</v>
+      </c>
+      <c r="E85">
+        <v>63</v>
+      </c>
+      <c r="F85">
+        <v>764</v>
+      </c>
+      <c r="H85">
+        <v>72605.5</v>
+      </c>
+      <c r="I85" t="s">
+        <v>104</v>
+      </c>
+      <c r="J85" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
